--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1395,247 +1395,283 @@
     <row r="16">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ chronos_model.py</t>
+          <t>│   │   ├─ timesfm_model.py</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr">
         <is>
-          <t>Zero-shot forecast + quantiles</t>
+          <t>TimesFM 2.5 zero-shot forecast + quantiles (v1 default)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="64" t="inlineStr">
         <is>
+          <t>│   │   ├─ chronos_model.py</t>
+        </is>
+      </c>
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Chronos-2 forecaster (alternative backbone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
           <t>│   │   └─ conformal.py</t>
         </is>
       </c>
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Split-conformal calibration wrapper</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>Split-conformal + CQR calibration wrapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>│   ├─ events/</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>Event reasoning layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="64" t="inlineStr">
-        <is>
-          <t>│   │   ├─ embed.py</t>
-        </is>
-      </c>
-      <c r="B19" s="65" t="inlineStr">
-        <is>
-          <t>Sentence-transformer embeddings</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ severity.py</t>
+          <t>│   │   ├─ embed.py</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>Rule-based severity tagging</t>
+          <t>Sentence-transformer embeddings</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="64" t="inlineStr">
         <is>
+          <t>│   │   ├─ severity.py</t>
+        </is>
+      </c>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>Rule-based severity tagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
           <t>│   │   └─ attribute.py</t>
         </is>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B22" s="63" t="inlineStr">
         <is>
           <t>relevance x severity x recency ranking</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="60" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>│   ├─ detect/</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>Structural-break layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="64" t="inlineStr">
-        <is>
-          <t>│   │   └─ changepoint.py</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="inlineStr">
-        <is>
-          <t>ruptures / BOCPD on residuals</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
+          <t>│   │   └─ changepoint.py</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>ruptures / BOCPD on residuals</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="64" t="inlineStr">
+        <is>
           <t>│   ├─ pipeline.py</t>
         </is>
       </c>
-      <c r="B24" s="63" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>Orchestrates forecast -&gt; monitor -&gt; attribute -&gt; alert</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="60" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>│   └─ eval/</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>Evaluation layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="62" t="inlineStr">
-        <is>
-          <t>│       ├─ backtest.py</t>
-        </is>
-      </c>
-      <c r="B26" s="63" t="inlineStr">
-        <is>
-          <t>Rolling-origin; coverage, MASE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
+          <t>│       ├─ backtest.py</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="inlineStr">
+        <is>
+          <t>Rolling-origin; coverage, MASE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
           <t>│       └─ event_eval.py</t>
         </is>
       </c>
-      <c r="B27" s="65" t="inlineStr">
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>Lead-time, precision/recall, attribution accuracy</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="60" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>├─ notebooks/</t>
         </is>
       </c>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>Analysis &amp; demo</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="64" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t>│   └─ 01_case_study_steel.ipynb</t>
         </is>
       </c>
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B30" s="63" t="inlineStr">
         <is>
           <t>The demo: dated example + charts</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>└─ outputs/</t>
+          <t>├─ scripts/</t>
         </is>
       </c>
       <c r="B31" s="61" t="inlineStr">
         <is>
-          <t>Generated artifacts</t>
+          <t>Runnable build-step scripts</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ figures/</t>
+          <t>│   └─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>Interval-breach plots for the writeup</t>
+          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Recommended build order (always keep something working)</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>└─ outputs/</t>
+        </is>
+      </c>
+      <c r="B34" s="61" t="inlineStr">
+        <is>
+          <t>Generated artifacts</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="64" t="inlineStr">
         <is>
+          <t xml:space="preserve">    └─ figures/</t>
+        </is>
+      </c>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>Interval-breach plots for the writeup</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Recommended build order (always keep something working)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
           <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
         <is>
           <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="64" t="inlineStr">
+      <c r="B39" s="36" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
         <is>
           <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="B41" s="36" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1645,12 +1681,12 @@
   <mergeCells count="8">
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2217,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2336,296 +2372,350 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>v1 backbone set to TimesFM 2.5 (quantile head) + CQR calibration; validated on SLX</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>For Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Design Authority</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>(owner)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Overall design sign-off</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Data / ML Lead</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Model + data feasibility</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Risk Stakeholder</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Business value &amp; metrics</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="17" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Zero-shot</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Forecasting a new series with a pretrained model, no per-series retraining.</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Large pretrained time-series model (Chronos-2, TimesFM, Moirai-2).</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Conformal prediction</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Wrapper giving prediction intervals with empirically guaranteed coverage.</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>CQR</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Conformalized Quantile Regression; offsets a model's q10/q90 band to hit target coverage.</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>TimesFM 2.5</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Google's 200M-param decoder-only time-series foundation model; zero-shot, quantile head.</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Fraction of actuals that fall inside the predicted interval (should match nominal, e.g. 90%).</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Interval breach</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Actual value falls outside the calibrated forecast interval -&gt; candidate shock.</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Changepoint</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Statistically detected structural break in a series (via PELT / BOCPD).</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Attribution</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Ranking candidate events to name the most likely driver of a break.</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Early-Warning System.</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>MASE</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Mean Absolute Scaled Error; scale-free forecast accuracy vs seasonal-naive.</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>FBX</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Freightos Baltic Index (container shipping cost).</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4640,12 +4730,12 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Chronos-2 (chosen)</t>
+          <t>TimesFM 2.5 (chosen)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>TimesFM</t>
+          <t>Chronos-2</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -4672,12 +4762,12 @@
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>Yes - quantile forecasts out of the box</t>
+          <t>Yes - continuous quantile head (deciles)</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Point-centric; add uncertainty yourself</t>
+          <t>Yes - quantile forecasts</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -4687,14 +4777,14 @@
       </c>
       <c r="F6" s="38" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>Tie</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>API / ecosystem maturity</t>
+          <t>Tooling / preflight for local run</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -4704,12 +4794,12 @@
       </c>
       <c r="C7" s="37" t="inlineStr">
         <is>
-          <t>Cleanest (AutoGluon integration)</t>
+          <t>Vetted skill + system preflight checker</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Clean (AutoGluon)</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4719,7 +4809,7 @@
       </c>
       <c r="F7" s="39" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>TimesFM 2.5</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4826,7 @@
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>Limited in v1 usage</t>
+          <t>Supported via XReg (v2)</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -4768,14 +4858,14 @@
       </c>
       <c r="C9" s="37" t="inlineStr">
         <is>
+          <t>200M, ~1.5 GB RAM, CPU-friendly</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
           <t>CPU / modest GPU</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Modest GPU</t>
-        </is>
-      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Modest-heavy GPU</t>
@@ -4783,39 +4873,39 @@
       </c>
       <c r="F9" s="39" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>TimesFM 2.5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Time-to-first-forecast</t>
+          <t>Context length</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>Fastest</t>
+          <t>Up to 16,384 points</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="F10" s="38" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>TimesFM 2.5</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4922,12 @@
       </c>
       <c r="C11" s="37" t="inlineStr">
         <is>
-          <t>Best overall for calibrated zero-shot</t>
+          <t>Best: calibrated zero-shot, CPU, ready tooling</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Strong point forecasts</t>
+          <t>Strong alternative</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -4847,7 +4937,7 @@
       </c>
       <c r="F11" s="39" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>TimesFM 2.5</t>
         </is>
       </c>
     </row>
@@ -4866,8 +4956,8 @@
     <row r="14">
       <c r="A14" s="37" t="inlineStr">
         <is>
-          <t>DECISION: Use Chronos-2 (Bolt variant) as the v1 forecasting backbone.
-WHY: It offers native quantile (probabilistic) output, the cleanest Python API, and the lowest compute footprint, which is the fastest path to a working calibrated-interval forecast, exactly the v1 goal. TimesFM is point-forecast-centric (you would bolt on uncertainty). Moirai-2 wins on multivariate covariate fusion and is therefore the planned v2 upgrade once macro covariates are added.</t>
+          <t>DECISION: Use TimesFM 2.5 (200M, PyTorch) as the v1 forecasting backbone.
+WHY: Its continuous quantile head returns calibrated decile intervals zero-shot, it is CPU-friendly (~1.5 GB RAM), and it ships a vetted skill plus a mandatory preflight checker for safe local inference. The raw q10/q90 band is then widened to the 90% target with split-conformal CQR (Romano 2019). Chronos-2 remains a drop-in alternative (kept in src/forecast/chronos_model.py); Moirai-2 stays the planned v2 upgrade for covariate fusion. This supersedes the v1.0 choice of Chronos-2: TimesFM 2.5's quantile head removes the earlier 'point-centric' objection.</t>
         </is>
       </c>
     </row>
@@ -4913,12 +5003,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Conformal prediction (MAPIE-style)</t>
+          <t>Split-conformal CQR (Romano 2019)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Turn raw quantiles into guaranteed-coverage intervals</t>
+          <t>Widen the q10/q90 band to guaranteed target coverage</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -5202,8 +5292,8 @@
       <c r="I6" s="2" t="n"/>
       <c r="K6" s="28" t="inlineStr">
         <is>
-          <t>Chronos-2 zero-shot
-→ quantile forecast</t>
+          <t>TimesFM 2.5 zero-shot
+quantile forecast</t>
         </is>
       </c>
       <c r="L6" s="2" t="n"/>
@@ -5323,8 +5413,8 @@
     <row r="10" ht="15" customHeight="1">
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>Conformal wrapper
-→ calibrated interval</t>
+          <t>Split-conformal CQR
+calibrated interval</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -6068,7 +6158,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>TimesFM 2.5 (Chronos-2 alt)</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -6078,12 +6168,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Quantile forecast</t>
+          <t>Quantile forecast (deciles)</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>src/forecast/chronos_model.py</t>
+          <t>src/forecast/timesfm_model.py</t>
         </is>
       </c>
     </row>
@@ -6095,17 +6185,17 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Conformal (MAPIE-style)</t>
+          <t>Split-conformal CQR</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Quantile forecast</t>
+          <t>Raw q10/q90 band</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Calibrated interval</t>
+          <t>Calibrated 90% interval</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -19,6 +19,7 @@
     <sheet name="8. File Structure" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="9. Evaluation &amp; Backtest" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10. NFRs &amp; Risks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="11. Build Log &amp; Validation" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -177,7 +178,7 @@
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -247,6 +248,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C6500"/>
       </patternFill>
     </fill>
   </fills>
@@ -418,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -592,6 +598,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2247,6 +2259,598 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Build Log &amp; Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>What has actually been built and measured, versus the documented goals</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Build progression (against the file-structure build order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Build order step</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>1. prices + forecaster</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Zero-shot forecast plotted</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>outputs/figures/*.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>2. conformal + backtest</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Calibrated intervals + coverage</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>step1_summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>3. events + attribution</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Event table + breach attribution</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="69" t="inlineStr">
+        <is>
+          <t>4. event eval</t>
+        </is>
+      </c>
+      <c r="B9" s="69" t="inlineStr">
+        <is>
+          <t>Lead-time / precision / attribution acc.</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D9" s="69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>after step 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="69" t="inlineStr">
+        <is>
+          <t>5. notebook + writeup</t>
+        </is>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>Shareable case study</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D10" s="69" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E10" s="69" t="inlineStr">
+        <is>
+          <t>README worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Step-1 goal verification (forecast + calibration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Goal / eval criterion</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Target / pass bar</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Measured result</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>G1 Calibrated forecast</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>90% interval covers ~90%</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>91.5% coverage</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>CQR offset Q=1.55 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>Interval calibration (headline)</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>coverage ~ nominal</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>raw 80% -&gt; 79.2%; cal -&gt; 91.5%</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>TimesFM deciles near-calibrated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="69" t="inlineStr">
+        <is>
+          <t>Forecast quality (MASE)</t>
+        </is>
+      </c>
+      <c r="B17" s="69" t="inlineStr">
+        <is>
+          <t>beat seasonal-naive</t>
+        </is>
+      </c>
+      <c r="C17" s="69" t="inlineStr">
+        <is>
+          <t>TimesFM 4.33 vs naive 4.21</t>
+        </is>
+      </c>
+      <c r="D17" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>Explained: efficient ETF ~ random walk</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="69" t="inlineStr">
+        <is>
+          <t>Baseline gauntlet</t>
+        </is>
+      </c>
+      <c r="B18" s="69" t="inlineStr">
+        <is>
+          <t>naive / ARIMA / GARCH</t>
+        </is>
+      </c>
+      <c r="C18" s="69" t="inlineStr">
+        <is>
+          <t>naive + ARIMA done</t>
+        </is>
+      </c>
+      <c r="D18" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E18" s="69" t="inlineStr">
+        <is>
+          <t>GARCH not yet implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="69" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="B19" s="69" t="inlineStr">
+        <is>
+          <t>frozen ~6-month holdout</t>
+        </is>
+      </c>
+      <c r="C19" s="69" t="inlineStr">
+        <is>
+          <t>rolling origins + 10d holdout</t>
+        </is>
+      </c>
+      <c r="D19" s="69" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>Frozen holdout still to add</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>G4 Checkable</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>dated, falsifiable, reproducible</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>dated example + script</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="inlineStr">
+        <is>
+          <t>step1_forecast_slx.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Step-1 measured results (SLX, 2016-01-04 to 2026-07-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Backbone / calibration</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>TimesFM 2.5 zero-shot + split-conformal CQR</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>10 business days</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Raw q10-q90 coverage (nominal 80%)</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>79.2%</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>CQR-calibrated coverage (target 90%)</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>91.5%</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>CQR offset Q</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>1.55 (USD)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>MASE  TimesFM / ARIMA / naive</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>4.33 / 4.22 / 4.21</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Headline holdout (2026-06-24 -&gt; 07-08)</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>0 interval breaches</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="70" t="inlineStr">
+        <is>
+          <t>Open gaps carried forward (do not drift, close these)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>•  GARCH volatility baseline: add to the gauntlet alongside ARIMA + seasonal-naive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>•  Frozen ~6-month holdout: implement the untouched holdout the design specifies for robustness.</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>•  Point accuracy vs naive: expected to improve on less-efficient targets (HRC futures, freight rates), not broad ETFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>•  Event layer (G2/G3): build-step 3 wires the Federal Register events + breach monitor + attribution.</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n"/>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B28:E28"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1599,7 +1599,7 @@
     <row r="32">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>│   └─ step1_forecast_slx.py</t>
+          <t>│   ├─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
@@ -1609,81 +1609,93 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B33" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
+      <c r="A33" s="64" t="inlineStr">
+        <is>
+          <t>│   └─ step2_events_attribution.py</t>
+        </is>
+      </c>
+      <c r="B33" s="65" t="inlineStr">
+        <is>
+          <t>Step 2: breach detection + Federal Register attribution</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="60" t="inlineStr">
         <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B34" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
           <t>└─ outputs/</t>
         </is>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>Generated artifacts</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="64" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B35" s="65" t="inlineStr">
+      <c r="B36" s="63" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="64" t="inlineStr">
+      <c r="B38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
         <is>
           <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="64" t="inlineStr">
+      <c r="B40" s="36" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="62" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="64" t="inlineStr">
+      <c r="B42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1693,9 +1705,9 @@
   <mergeCells count="8">
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
@@ -2265,7 +2277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2378,56 +2390,56 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>3. events + attribution</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Event table + breach attribution</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>step2_summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>4. event eval</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Lead-time / precision / attribution acc.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Next</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>in progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="69" t="inlineStr">
-        <is>
-          <t>4. event eval</t>
-        </is>
-      </c>
-      <c r="B9" s="69" t="inlineStr">
-        <is>
-          <t>Lead-time / precision / attribution acc.</t>
-        </is>
-      </c>
-      <c r="C9" s="69" t="inlineStr">
-        <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="D9" s="69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="69" t="inlineStr">
-        <is>
-          <t>after step 3</t>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>forward eval pending</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2466,7 @@
       </c>
       <c r="E10" s="69" t="inlineStr">
         <is>
-          <t>README worked example</t>
+          <t>README worked examples</t>
         </is>
       </c>
     </row>
@@ -2782,68 +2794,195 @@
       <c r="E31" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="70" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Step-2 measured results (event attribution, retrospective)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Events (Federal Register proclamations + rules)</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>255 (2018-02 to 2026-06)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Full-sample CQR realized coverage</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>90.1% (target 90%, Q=0.73)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Breach-days flagged</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>209 / 2110 (~10% tail)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Volatility-regime changepoints</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>18 (2020 crash, 2022, 2025 turmoil)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Breaches w/ tariff event in 14d vs base rate</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>72% vs 66% (density-driven, honest)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Dated example</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>2022-06-13 breach -&gt; 2022-06-03 steel proclamation (rel 0.64)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="70" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>•  GARCH volatility baseline: add to the gauntlet alongside ARIMA + seasonal-naive.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>•  Frozen ~6-month holdout: implement the untouched holdout the design specifies for robustness.</t>
         </is>
       </c>
-      <c r="B36" s="36" t="n"/>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="B46" s="36" t="n"/>
+      <c r="C46" s="36" t="n"/>
+      <c r="D46" s="36" t="n"/>
+      <c r="E46" s="36" t="n"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>•  Point accuracy vs naive: expected to improve on less-efficient targets (HRC futures, freight rates), not broad ETFs.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>•  Event layer (G2/G3): build-step 3 wires the Federal Register events + breach monitor + attribution.</t>
-        </is>
-      </c>
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>•  Attribution signal: hit-rate (72%) barely beats event-density base rate (66%); needs tighter windows / high-severity-only events to be causal, not coincidental.</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>•  Forward event eval (G3): step-2 is retrospective; still need lead-time / precision / attribution-accuracy on a forward split.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="23">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -424,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -602,6 +602,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1239,7 +1245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1611,7 +1617,7 @@
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>│   └─ step2_events_attribution.py</t>
+          <t>│   ├─ step2_events_attribution.py</t>
         </is>
       </c>
       <c r="B33" s="65" t="inlineStr">
@@ -1621,81 +1627,93 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B34" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
+      <c r="A34" s="62" t="inlineStr">
+        <is>
+          <t>│   └─ step3_close_gaps.py</t>
+        </is>
+      </c>
+      <c r="B34" s="63" t="inlineStr">
+        <is>
+          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="60" t="inlineStr">
         <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B35" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
           <t>└─ outputs/</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>Generated artifacts</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="B39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="64" t="inlineStr">
         <is>
           <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="62" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="64" t="inlineStr">
+      <c r="B41" s="36" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
         <is>
           <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="62" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="64" t="inlineStr">
+      <c r="B43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1703,11 +1721,11 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A39:B39"/>
@@ -2277,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2586,56 +2604,56 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="69" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Baseline gauntlet</t>
         </is>
       </c>
-      <c r="B18" s="69" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>naive / ARIMA / GARCH</t>
         </is>
       </c>
-      <c r="C18" s="69" t="inlineStr">
-        <is>
-          <t>naive + ARIMA done</t>
-        </is>
-      </c>
-      <c r="D18" s="69" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E18" s="69" t="inlineStr">
-        <is>
-          <t>GARCH not yet implemented</t>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>naive + ARIMA + GARCH(1,1)</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>GARCH added (step3), 87.5% holdout cov</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="69" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Robustness</t>
         </is>
       </c>
-      <c r="B19" s="69" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>frozen ~6-month holdout</t>
         </is>
       </c>
-      <c r="C19" s="69" t="inlineStr">
-        <is>
-          <t>rolling origins + 10d holdout</t>
-        </is>
-      </c>
-      <c r="D19" s="69" t="inlineStr">
-        <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>Frozen holdout still to add</t>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>frozen 2026 holdout + ACI</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>fixed 80% fwd -&gt; ACI holds ~90%</t>
         </is>
       </c>
     </row>
@@ -2906,83 +2924,214 @@
       <c r="E41" s="20" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="70" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Gap closure (literature-backed methods)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Method (source)</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>A. Frozen holdout</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Untouched trailing 6-mo (2026)</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Fixed CQR 80% fwd coverage (under-covers)</t>
+        </is>
+      </c>
+      <c r="D46" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>B. Regime-robust calibration</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Adaptive Conformal Inference (Gibbs &amp; Candes 2021)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Holds ~90%, far more stable than fixed offset</t>
+        </is>
+      </c>
+      <c r="D47" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>C. GARCH baseline</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>GARCH(1,1) volatility band (arch)</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>87.5% holdout coverage (beat fixed offset fwd)</t>
+        </is>
+      </c>
+      <c r="D48" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>D. Attribution significance</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Event-study circular-shift permutation test</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>72.2% vs 66.0% base, p=0.134 -&gt; not significant</t>
+        </is>
+      </c>
+      <c r="D49" s="71" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>E. Point vs naive</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>TSFM benchmarks (arxiv 2601.06371, cloud FM study)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Expected on efficient daily prices; not a bug</t>
+        </is>
+      </c>
+      <c r="D50" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="72" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>•  GARCH volatility baseline: add to the gauntlet alongside ARIMA + seasonal-naive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>•  Frozen ~6-month holdout: implement the untouched holdout the design specifies for robustness.</t>
-        </is>
-      </c>
-      <c r="B46" s="36" t="n"/>
-      <c r="C46" s="36" t="n"/>
-      <c r="D46" s="36" t="n"/>
-      <c r="E46" s="36" t="n"/>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>•  Point accuracy vs naive: expected to improve on less-efficient targets (HRC futures, freight rates), not broad ETFs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>•  Attribution signal: hit-rate (72%) barely beats event-density base rate (66%); needs tighter windows / high-severity-only events to be causal, not coincidental.</t>
-        </is>
-      </c>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>•  Forward event eval (G3): step-2 is retrospective; still need lead-time / precision / attribution-accuracy on a forward split.</t>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>•  Attribution not yet significant on the broad ETF (p=0.134): retry on a less-efficient target (HRC futures / freight rates) and high-severity-only events with tighter windows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>•  Forward event eval (G3): lead-time / precision on a forward (not retrospective) split, using ACI online calibration.</t>
+        </is>
+      </c>
+      <c r="B55" s="36" t="n"/>
+      <c r="C55" s="36" t="n"/>
+      <c r="D55" s="36" t="n"/>
+      <c r="E55" s="36" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>•  Promote ACI + GARCH from validation scripts into the live pipeline path (currently proven in scripts/step3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="27">
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="A48:E48"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B35:E35"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="D49:E49"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="B31:E31"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B37:E37"/>
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -424,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -607,6 +607,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1245,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1629,7 +1632,7 @@
     <row r="34">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>│   └─ step3_close_gaps.py</t>
+          <t>│   ├─ step3_close_gaps.py</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
@@ -1639,81 +1642,93 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B35" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>│   └─ step4_hrc_attribution.py</t>
+        </is>
+      </c>
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>Step 4: pre-registered attribution retest on HRC futures</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="60" t="inlineStr">
         <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B36" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
           <t>└─ outputs/</t>
         </is>
       </c>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>Generated artifacts</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="64" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B37" s="65" t="inlineStr">
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="64" t="inlineStr">
+      <c r="B40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="62" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="64" t="inlineStr">
+      <c r="B42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
         <is>
           <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="62" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="62" t="inlineStr">
         <is>
           <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="64" t="inlineStr">
+      <c r="B44" s="36" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1725,10 +1740,10 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2295,7 +2310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3068,44 +3083,67 @@
       </c>
       <c r="E50" s="8" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="72" t="inlineStr">
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>F. Attribution retest (HRC)</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Pre-registered primary: HRC=F, sev&gt;=0.7 events, 5d window, ACI online</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>hit 2.4% vs base 2.2%, p=0.46 -&gt; still not significant; diagnosis: 11-event low power + FR publication date lags market-moving announcement</t>
+        </is>
+      </c>
+      <c r="D51" s="72" t="inlineStr">
+        <is>
+          <t>Closed-Negative</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="73" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>•  Attribution not yet significant on the broad ETF (p=0.134): retry on a less-efficient target (HRC futures / freight rates) and high-severity-only events with tighter windows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>•  Causal attribution claim DEFERRED (evidence-based): retested on HRC=F with high-severity events + 5d pre-registered window, still not significant (p=0.46). Requires announcement-dated events (news/GDELT with FR as verification anchor) - the stubbed v2 news layer. Attribution ships as verifiable candidate-surfacing only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>•  Forward event eval (G3): lead-time / precision on a forward (not retrospective) split, using ACI online calibration.</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n"/>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="36" t="n"/>
-      <c r="E55" s="36" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="B56" s="36" t="n"/>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>•  Promote ACI + GARCH from validation scripts into the live pipeline path (currently proven in scripts/step3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="A1:E1"/>
@@ -3125,10 +3163,11 @@
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A53:E53"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="D50:E50"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1644,7 +1644,7 @@
     <row r="35">
       <c r="A35" s="64" t="inlineStr">
         <is>
-          <t>│   └─ step4_hrc_attribution.py</t>
+          <t>│   ├─ step4_hrc_attribution.py</t>
         </is>
       </c>
       <c r="B35" s="65" t="inlineStr">
@@ -1654,81 +1654,93 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B36" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
+      <c r="A36" s="62" t="inlineStr">
+        <is>
+          <t>│   └─ step5_forward_eval.py</t>
+        </is>
+      </c>
+      <c r="B36" s="63" t="inlineStr">
+        <is>
+          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="60" t="inlineStr">
         <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
           <t>└─ outputs/</t>
         </is>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>Generated artifacts</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="B39" s="65" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="64" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="64" t="inlineStr">
         <is>
           <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="62" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="64" t="inlineStr">
+      <c r="B43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr">
         <is>
           <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="62" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="62" t="inlineStr">
         <is>
           <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="64" t="inlineStr">
+      <c r="B45" s="36" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1741,9 +1753,9 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2310,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2450,29 +2462,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>4. event eval</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Lead-time / precision / attribution acc.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Next</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>forward eval pending</t>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>step5_forward_eval.json</t>
         </is>
       </c>
     </row>
@@ -3106,44 +3118,67 @@
       </c>
       <c r="E51" s="8" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="73" t="inlineStr">
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>G. Forward event eval (G3)</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Signals-approach EWS on 2024-07..2026-07 forward split, ACI flags, pre-forward-fixed shock threshold (rolling-2y sensitivity identical)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>1 shock onset (2025-02-26, Feb-2025 tariff reinstatement): flagged at onset (lead 0d), candidate proclamation surfaced (pub. 8d before); precision 3.6% honest false-alarm rate; n=1 -&gt; case study, no rate claims</t>
+        </is>
+      </c>
+      <c r="D52" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="73" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="14" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>•  Causal attribution claim DEFERRED (evidence-based): retested on HRC=F with high-severity events + 5d pre-registered window, still not significant (p=0.46). Requires announcement-dated events (news/GDELT with FR as verification anchor) - the stubbed v2 news layer. Attribution ships as verifiable candidate-surfacing only.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>•  Forward event eval (G3): lead-time / precision on a forward (not retrospective) split, using ACI online calibration.</t>
-        </is>
-      </c>
-      <c r="B56" s="36" t="n"/>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>•  Alert precision (3.6% on forward eval): most ACI flags mark small moves that never become sustained shocks. Candidate fixes to test forward, not post-hoc: require changepoint agreement or multi-day breach runs before alerting.</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n"/>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>•  Promote ACI + GARCH from validation scripts into the live pipeline path (currently proven in scripts/step3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="A1:E1"/>
@@ -3153,8 +3188,8 @@
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B41:E41"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="A54:E54"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="D48:E48"/>
@@ -3171,6 +3206,7 @@
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="D50:E50"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3141,41 +3141,57 @@
       </c>
       <c r="E52" s="8" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="73" t="inlineStr">
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>H. ACI + GARCH promoted to live pipeline</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>src/pipeline.py production path: incremental band-history cache (parquet), ACI online calibration, GARCH(1,1) + changepoint cross-checks on alerts, attribution as candidate-surfacing</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Verified end-to-end via python -m src.pipeline; alerts carry garch_agrees / changepoint_agrees / ACI coverage</t>
+        </is>
+      </c>
+      <c r="D53" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="73" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>•  Causal attribution claim DEFERRED (evidence-based): retested on HRC=F with high-severity events + 5d pre-registered window, still not significant (p=0.46). Requires announcement-dated events (news/GDELT with FR as verification anchor) - the stubbed v2 news layer. Attribution ships as verifiable candidate-surfacing only.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t>•  Alert precision (3.6% on forward eval): most ACI flags mark small moves that never become sustained shocks. Candidate fixes to test forward, not post-hoc: require changepoint agreement or multi-day breach runs before alerting.</t>
-        </is>
-      </c>
-      <c r="B57" s="36" t="n"/>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>•  Promote ACI + GARCH from validation scripts into the live pipeline path (currently proven in scripts/step3).</t>
-        </is>
-      </c>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>•  Alert precision (3.6% on forward eval): most ACI flags mark small moves that never become sustained shocks. Candidate fixes to test forward, not post-hoc: require changepoint agreement or multi-day breach runs before alerting (both flags now carried on every Alert by the live pipeline).</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="n"/>
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3194,10 +3210,10 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="A56:E56"/>
+    <mergeCell ref="D53:E53"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B39:E39"/>
@@ -6380,8 +6396,8 @@
     <row r="10" ht="15" customHeight="1">
       <c r="K10" s="28" t="inlineStr">
         <is>
-          <t>Split-conformal CQR
-calibrated interval</t>
+          <t>ACI online calibration
+(CQR offline)</t>
         </is>
       </c>
       <c r="L10" s="2" t="n"/>
@@ -7012,7 +7028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7147,22 +7163,22 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Calibrator</t>
+          <t>Calibrator (live)</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Split-conformal CQR</t>
+          <t>ACI online (CQR for offline studies)</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Raw q10/q90 band</t>
+          <t>Raw q10/q90 band history</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Calibrated 90% interval</t>
+          <t>Calibrated 90% interval, regime-robust</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -7174,160 +7190,214 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Breach monitor</t>
+          <t>GARCH cross-check</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>NumPy logic</t>
+          <t>GARCH(1,1) band (arch)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Actuals + interval</t>
+          <t>Price history</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Breach flags</t>
+          <t>Independent volatility band, garch_agrees flag</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>src/pipeline.py</t>
+          <t>src/eval/backtest.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Changepoint</t>
+          <t>Band history cache</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>ruptures / BOCPD</t>
+          <t>Parquet incremental cache</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Forecast residuals</t>
+          <t>New H-day blocks only</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Changepoint indices</t>
+          <t>data/bands_&lt;vertical&gt;.parquet</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>src/detect/changepoint.py</t>
+          <t>src/pipeline.py</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Event embedder</t>
+          <t>Breach monitor</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>sentence-transformers</t>
+          <t>NumPy logic</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Event text</t>
+          <t>Actuals + interval</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Embeddings + relevance</t>
+          <t>Breach flags</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>src/events/embed.py</t>
+          <t>src/pipeline.py</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Severity tagger</t>
+          <t>Changepoint</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Rule engine</t>
+          <t>ruptures / BOCPD</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Event text</t>
+          <t>Forecast residuals</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Severity score</t>
+          <t>Changepoint indices</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>src/events/severity.py</t>
+          <t>src/detect/changepoint.py</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Attribution</t>
+          <t>Event embedder</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>sentence-transformers</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Events + breach + changepoint</t>
+          <t>Event text</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Top driver + link</t>
+          <t>Embeddings + relevance</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>src/events/attribute.py</t>
+          <t>src/events/embed.py</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
+          <t>Severity tagger</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Rule engine</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Event text</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Severity score</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>src/events/severity.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Attribution</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Events + breach + changepoint</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Top driver + link</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>src/events/attribute.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Evaluator</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>pandas / metrics</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Forecasts, events, labels</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Coverage, MASE, lead time, attr acc</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>src/eval/*</t>
         </is>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1392,7 @@
     <row r="14">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>│   │   └─ events.py</t>
+          <t>│   │   ├─ events.py</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr">
@@ -1402,360 +1402,408 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
-        <is>
-          <t>│   ├─ forecast/</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="inlineStr">
-        <is>
-          <t>Forecasting layer</t>
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>│   │   ├─ news_tpu.py</t>
+        </is>
+      </c>
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Daily TPU index (announcement-dated events, primary)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ timesfm_model.py</t>
+          <t>│   │   └─ news_gdelt.py</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr">
         <is>
-          <t>TimesFM 2.5 zero-shot forecast + quantiles (v1 default)</t>
+          <t>GDELT volume spikes (fallback; API throttles)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="64" t="inlineStr">
-        <is>
-          <t>│   │   ├─ chronos_model.py</t>
-        </is>
-      </c>
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Chronos-2 forecaster (alternative backbone)</t>
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>│   ├─ forecast/</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>Forecasting layer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="62" t="inlineStr">
         <is>
-          <t>│   │   └─ conformal.py</t>
+          <t>│   │   ├─ timesfm_model.py</t>
         </is>
       </c>
       <c r="B18" s="63" t="inlineStr">
         <is>
-          <t>Split-conformal + CQR calibration wrapper</t>
+          <t>TimesFM 2.5 zero-shot forecast + quantiles (v1 default)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>│   ├─ events/</t>
-        </is>
-      </c>
-      <c r="B19" s="61" t="inlineStr">
-        <is>
-          <t>Event reasoning layer</t>
+      <c r="A19" s="64" t="inlineStr">
+        <is>
+          <t>│   │   ├─ chronos_model.py</t>
+        </is>
+      </c>
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Chronos-2 forecaster (alternative backbone)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ embed.py</t>
+          <t>│   │   └─ conformal.py</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>Sentence-transformer embeddings</t>
+          <t>Split-conformal + CQR calibration wrapper</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>│   │   ├─ severity.py</t>
-        </is>
-      </c>
-      <c r="B21" s="65" t="inlineStr">
-        <is>
-          <t>Rule-based severity tagging</t>
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>│   ├─ events/</t>
+        </is>
+      </c>
+      <c r="B21" s="61" t="inlineStr">
+        <is>
+          <t>Event reasoning layer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>│   │   └─ attribute.py</t>
+          <t>│   │   ├─ embed.py</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>relevance x severity x recency ranking</t>
+          <t>Sentence-transformer embeddings</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
-        <is>
-          <t>│   ├─ detect/</t>
-        </is>
-      </c>
-      <c r="B23" s="61" t="inlineStr">
-        <is>
-          <t>Structural-break layer</t>
+      <c r="A23" s="64" t="inlineStr">
+        <is>
+          <t>│   │   ├─ severity.py</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>Rule-based severity tagging</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
+          <t>│   │   └─ attribute.py</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>relevance x severity x recency ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>│   ├─ detect/</t>
+        </is>
+      </c>
+      <c r="B25" s="61" t="inlineStr">
+        <is>
+          <t>Structural-break layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
           <t>│   │   └─ changepoint.py</t>
         </is>
       </c>
-      <c r="B24" s="63" t="inlineStr">
+      <c r="B26" s="63" t="inlineStr">
         <is>
           <t>ruptures / BOCPD on residuals</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="64" t="inlineStr">
-        <is>
-          <t>│   ├─ pipeline.py</t>
-        </is>
-      </c>
-      <c r="B25" s="65" t="inlineStr">
-        <is>
-          <t>Orchestrates forecast -&gt; monitor -&gt; attribute -&gt; alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
-          <t>│   └─ eval/</t>
-        </is>
-      </c>
-      <c r="B26" s="61" t="inlineStr">
-        <is>
-          <t>Evaluation layer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
+          <t>│   ├─ pipeline.py</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="inlineStr">
+        <is>
+          <t>Orchestrates forecast -&gt; monitor -&gt; attribute -&gt; alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>│   └─ eval/</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="inlineStr">
+        <is>
+          <t>Evaluation layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="64" t="inlineStr">
+        <is>
           <t>│       ├─ backtest.py</t>
         </is>
       </c>
-      <c r="B27" s="65" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>Rolling-origin; coverage, MASE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t>│       └─ event_eval.py</t>
-        </is>
-      </c>
-      <c r="B28" s="63" t="inlineStr">
-        <is>
-          <t>Lead-time, precision/recall, attribution accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="60" t="inlineStr">
-        <is>
-          <t>├─ notebooks/</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="inlineStr">
-        <is>
-          <t>Analysis &amp; demo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="62" t="inlineStr">
         <is>
-          <t>│   └─ 01_case_study_steel.ipynb</t>
+          <t>│       └─ event_eval.py</t>
         </is>
       </c>
       <c r="B30" s="63" t="inlineStr">
         <is>
-          <t>The demo: dated example + charts</t>
+          <t>Lead-time, precision/recall, attribution accuracy</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>├─ scripts/</t>
+          <t>├─ notebooks/</t>
         </is>
       </c>
       <c r="B31" s="61" t="inlineStr">
         <is>
-          <t>Runnable build-step scripts</t>
+          <t>Analysis &amp; demo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step1_forecast_slx.py</t>
+          <t>│   └─ 01_case_study_steel.ipynb</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
+          <t>The demo: dated example + charts</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="64" t="inlineStr">
-        <is>
-          <t>│   ├─ step2_events_attribution.py</t>
-        </is>
-      </c>
-      <c r="B33" s="65" t="inlineStr">
-        <is>
-          <t>Step 2: breach detection + Federal Register attribution</t>
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>├─ scripts/</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="inlineStr">
+        <is>
+          <t>Runnable build-step scripts</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step3_close_gaps.py</t>
+          <t>│   ├─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
+          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step4_hrc_attribution.py</t>
+          <t>│   ├─ step2_events_attribution.py</t>
         </is>
       </c>
       <c r="B35" s="65" t="inlineStr">
         <is>
-          <t>Step 4: pre-registered attribution retest on HRC futures</t>
+          <t>Step 2: breach detection + Federal Register attribution</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>│   └─ step5_forward_eval.py</t>
+          <t>│   ├─ step3_close_gaps.py</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
+          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t>│   ├─ step4_hrc_attribution.py</t>
+        </is>
+      </c>
+      <c r="B37" s="65" t="inlineStr">
+        <is>
+          <t>Step 4: pre-registered attribution retest on HRC futures</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="62" t="inlineStr">
+        <is>
+          <t>│   ├─ step5_forward_eval.py</t>
+        </is>
+      </c>
+      <c r="B38" s="63" t="inlineStr">
+        <is>
           <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B37" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="60" t="inlineStr">
-        <is>
-          <t>└─ outputs/</t>
-        </is>
-      </c>
-      <c r="B38" s="61" t="inlineStr">
-        <is>
-          <t>Generated artifacts</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
+          <t>│   ├─ step6_announcement_attribution.py</t>
+        </is>
+      </c>
+      <c r="B39" s="65" t="inlineStr">
+        <is>
+          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
+        <is>
+          <t>│   └─ step7_alert_precision.py</t>
+        </is>
+      </c>
+      <c r="B40" s="63" t="inlineStr">
+        <is>
+          <t>Step 7: pre-specified alert-precision filter evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B41" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>└─ outputs/</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="inlineStr">
+        <is>
+          <t>Generated artifacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B39" s="65" t="inlineStr">
+      <c r="B43" s="65" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="64" t="inlineStr">
-        <is>
-          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="62" t="inlineStr">
-        <is>
-          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
-        </is>
-      </c>
-      <c r="B43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="64" t="inlineStr">
-        <is>
-          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="62" t="inlineStr">
-        <is>
-          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
-        </is>
-      </c>
-      <c r="B45" s="36" t="n"/>
+      <c r="B45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="64" t="inlineStr">
         <is>
+          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr">
+        <is>
+          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="64" t="inlineStr">
+        <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2322,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3164,38 +3212,62 @@
       </c>
       <c r="E53" s="8" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="73" t="inlineStr">
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>I. Announcement-dated retest (TPU)</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Daily TPU index (Caldara-Iacoviello JME 2020) spike onsets, validated vs known announcements; identical pre-registered design as step 4; GDELT implemented as fallback (API hard-throttles)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY p=0.85 (hit 6.8% vs base 9.0%); all sensitivity cells null. Causal attribution REJECTED under both event datings -&gt; permanently ships as candidate-surfacing; no further sources tried (would be p-hacking)</t>
+        </is>
+      </c>
+      <c r="D54" s="72" t="inlineStr">
+        <is>
+          <t>Closed-Negative</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="73" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>•  Causal attribution claim DEFERRED (evidence-based): retested on HRC=F with high-severity events + 5d pre-registered window, still not significant (p=0.46). Requires announcement-dated events (news/GDELT with FR as verification anchor) - the stubbed v2 news layer. Attribution ships as verifiable candidate-surfacing only.</t>
-        </is>
-      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
-        <is>
-          <t>•  Alert precision (3.6% on forward eval): most ACI flags mark small moves that never become sustained shocks. Candidate fixes to test forward, not post-hoc: require changepoint agreement or multi-day breach runs before alerting (both flags now carried on every Alert by the live pipeline).</t>
-        </is>
-      </c>
-      <c r="B58" s="36" t="n"/>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>•  Causal attribution: CLOSED as rejected (two pre-registered nulls: FR-dated p=0.46, TPU announcement-dated p=0.85). Attribution permanently ships as candidate-surfacing with a source link; no further event sources will be tried against this hypothesis (p-hacking).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>•  Alert precision (3.6% on forward eval): pre-specified filters (changepoint agreement, multi-day breach runs) under evaluation in step 7; config knobs to follow from the evaluated numbers.</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="n"/>
+      <c r="C59" s="36" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="B40:E40"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="D46:E46"/>
@@ -3209,7 +3281,6 @@
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="A56:E56"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="D47:E47"/>
@@ -3220,6 +3291,7 @@
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="D54:E54"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="A58:E58"/>
@@ -5340,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5560,87 +5632,119 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>Event stream (announcement-dated)</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Daily TPU index (Caldara-Iacoviello, JME 2020)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>XLSX download, no key</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Daily (updated ~monthly)</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Expert newspaper-count index; spikes are announcement-dated. Primary news layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>Event stream (supplement)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>News headlines (GDELT / NewsAPI free tier)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>REST API</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Free tier</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>GDELT news-volume spikes (EPU-style)</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>GDELT DOC 2.0 API</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Breadth on geopolitics; noisier, used to supplement not anchor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Fallback: API hard-throttles multi-year pulls; incremental cache implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Design decisions &amp; data governance</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>•  The Federal Register API is the anchor of the whole project: free, structured JSON, timestamped, and queryable by agency + date + keyword. It makes 'which event caused the break' auditable rather than hand-wavy.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>•  All sources are free / public. No proprietary or licensed market feeds are required for v1, so the repo is fully reproducible by a reviewer.</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>•  Raw pulls are cached to gitignored parquet; only derived, shareable artifacts are committed.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>•  A frozen holdout window (most recent ~6 months) is never touched during development to keep the backtest honest.</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>•  Rate limits: batch pulls, cache aggressively, and stamp each record with a pull timestamp for reproducibility.</t>
         </is>
@@ -5654,7 +5758,7 @@
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -2370,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3235,43 +3235,75 @@
       </c>
       <c r="E54" s="8" t="n"/>
     </row>
-    <row r="57">
-      <c r="A57" s="73" t="inlineStr">
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>J. Alert-precision filters</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Pre-specified F1 (changepoint agreement +/-7d) and F2 (breach run&gt;=2), KLR persistence-filter practice; evaluated on the step-5 forward window</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>F1: 55-&gt;6 flags, precision 3.6%-&gt;33.3%, NSR 0.84-&gt;0.08, recall preserved 1/1 -&gt; live default ON. F2: dropped the only true positive (gap-style shock) -&gt; OFF. n=1 caveat recorded</t>
+        </is>
+      </c>
+      <c r="D55" s="70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="73" t="inlineStr">
         <is>
           <t>Open gaps carried forward (do not drift, close these)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>•  Causal attribution: CLOSED as rejected (two pre-registered nulls: FR-dated p=0.46, TPU announcement-dated p=0.85). Attribution permanently ships as candidate-surfacing with a source link; no further event sources will be tried against this hypothesis (p-hacking).</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>•  Alert precision (3.6% on forward eval): pre-specified filters (changepoint agreement, multi-day breach runs) under evaluation in step 7; config knobs to follow from the evaluated numbers.</t>
-        </is>
-      </c>
-      <c r="B59" s="36" t="n"/>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="36" t="n"/>
-      <c r="E59" s="36" t="n"/>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>•  Alert precision: CLOSED. F1 changepoint-agreement filter live by default (NSR 0.84-&gt;0.08, recall preserved); F2 persistence filter evaluated harmful and disabled. Revisit both as more forward shocks accrue (current evidence is n=1).</t>
+        </is>
+      </c>
+      <c r="B60" s="36" t="n"/>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="36" t="n"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>•  Remaining v2 items (not gaps): Moirai-2 covariate backbone, additional verticals via new YAML, streaming alert delivery.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="32">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B26:E26"/>
@@ -3285,9 +3317,9 @@
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="B29:E29"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>1.0 (Draft for review)</t>
+          <t>1.2 (v1 delivered)</t>
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Baseline design - v1 scope frozen</t>
+          <t>v1 complete: pipeline live, all logged gaps closed with evidence</t>
         </is>
       </c>
       <c r="D17" s="8" t="n"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D18" s="8" t="n"/>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B7" s="65" t="inlineStr">
         <is>
-          <t>uv/poetry deps: chronos, mapie, ruptures, sentence-transformers</t>
+          <t>deps: timesfm[torch], arch, ruptures, sentence-transformers (chronos optional)</t>
         </is>
       </c>
     </row>
@@ -1613,182 +1613,206 @@
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>The demo: dated example + charts</t>
+          <t>Interactive walkthrough of the production path</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>├─ scripts/</t>
+          <t>├─ tools/</t>
         </is>
       </c>
       <c r="B33" s="61" t="inlineStr">
         <is>
-          <t>Runnable build-step scripts</t>
+          <t>Repo meta-tooling</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step1_forecast_slx.py</t>
+          <t>│   └─ build_design_doc.py</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
+          <t>Regenerates docs/ solution design workbook</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="64" t="inlineStr">
-        <is>
-          <t>│   ├─ step2_events_attribution.py</t>
-        </is>
-      </c>
-      <c r="B35" s="65" t="inlineStr">
-        <is>
-          <t>Step 2: breach detection + Federal Register attribution</t>
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>├─ scripts/</t>
+        </is>
+      </c>
+      <c r="B35" s="61" t="inlineStr">
+        <is>
+          <t>Runnable build-step scripts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step3_close_gaps.py</t>
+          <t>│   ├─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
+          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step4_hrc_attribution.py</t>
+          <t>│   ├─ step2_events_attribution.py</t>
         </is>
       </c>
       <c r="B37" s="65" t="inlineStr">
         <is>
-          <t>Step 4: pre-registered attribution retest on HRC futures</t>
+          <t>Step 2: breach detection + Federal Register attribution</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step5_forward_eval.py</t>
+          <t>│   ├─ step3_close_gaps.py</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
+          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step6_announcement_attribution.py</t>
+          <t>│   ├─ step4_hrc_attribution.py</t>
         </is>
       </c>
       <c r="B39" s="65" t="inlineStr">
         <is>
-          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+          <t>Step 4: pre-registered attribution retest on HRC futures</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="62" t="inlineStr">
         <is>
+          <t>│   ├─ step5_forward_eval.py</t>
+        </is>
+      </c>
+      <c r="B40" s="63" t="inlineStr">
+        <is>
+          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>│   ├─ step6_announcement_attribution.py</t>
+        </is>
+      </c>
+      <c r="B41" s="65" t="inlineStr">
+        <is>
+          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="62" t="inlineStr">
+        <is>
           <t>│   └─ step7_alert_precision.py</t>
         </is>
       </c>
-      <c r="B40" s="63" t="inlineStr">
+      <c r="B42" s="63" t="inlineStr">
         <is>
           <t>Step 7: pre-specified alert-precision filter evaluation</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>├─ data/</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>Gitignored raw + parquet cache</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="60" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>└─ outputs/</t>
         </is>
       </c>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>Generated artifacts</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="64" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">    └─ figures/</t>
         </is>
       </c>
-      <c r="B43" s="65" t="inlineStr">
+      <c r="B45" s="65" t="inlineStr">
         <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="64" t="inlineStr">
-        <is>
-          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="62" t="inlineStr">
-        <is>
-          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
-        </is>
-      </c>
-      <c r="B47" s="36" t="n"/>
+      <c r="B47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="64" t="inlineStr">
         <is>
-          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
+          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="62" t="inlineStr">
         <is>
-          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
+          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
         </is>
       </c>
       <c r="B49" s="36" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="64" t="inlineStr">
+        <is>
+          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="62" t="inlineStr">
+        <is>
+          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1798,10 +1822,10 @@
   <mergeCells count="8">
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A50:B50"/>
   </mergeCells>
@@ -3340,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3481,310 +3505,332 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>v1 delivered: ACI+GARCH pipeline live with F1 alert filter; causal attribution closed-rejected (two pre-registered nulls); Build Log rows A-J complete</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>v1 Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Design Authority</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>(owner)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Overall design sign-off</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Data / ML Lead</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Model + data feasibility</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Risk Stakeholder</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Business value &amp; metrics</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="17" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Zero-shot</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Forecasting a new series with a pretrained model, no per-series retraining.</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Large pretrained time-series model (Chronos-2, TimesFM, Moirai-2).</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Conformal prediction</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Wrapper giving prediction intervals with empirically guaranteed coverage.</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>CQR</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Conformalized Quantile Regression; offsets a model's q10/q90 band to hit target coverage.</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>TimesFM 2.5</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Google's 200M-param decoder-only time-series foundation model; zero-shot, quantile head.</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Fraction of actuals that fall inside the predicted interval (should match nominal, e.g. 90%).</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Interval breach</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Actual value falls outside the calibrated forecast interval -&gt; candidate shock.</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Changepoint</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Statistically detected structural break in a series (via PELT / BOCPD).</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Attribution</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Ranking candidate events to name the most likely driver of a break.</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Early-Warning System.</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>MASE</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Mean Absolute Scaled Error; scale-free forecast accuracy vs seasonal-naive.</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>FBX</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Freightos Baltic Index (container shipping cost).</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3796,10 +3842,10 @@
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B32:E32"/>
@@ -5257,7 +5303,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Chronos-2 zero-shot forecast, wrapped in conformal calibration for intervals.</t>
+          <t>TimesFM 2.5 zero-shot forecast, calibrated online with ACI for intervals.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -20,6 +20,7 @@
     <sheet name="9. Evaluation &amp; Backtest" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="10. NFRs &amp; Risks" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="11. Build Log &amp; Validation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="12. v2 Plan &amp; Progress" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -613,6 +614,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1105,7 +1112,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>1.2 (v1 delivered)</t>
+          <t>1.3 (v2 in progress)</t>
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
@@ -1120,7 +1127,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>v1 complete: pipeline live, all logged gaps closed with evidence</t>
+          <t>v1 complete and live; v2 workstreams W1-W3 planned on sheet 12</t>
         </is>
       </c>
       <c r="D17" s="8" t="n"/>
@@ -3358,13 +3365,218 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>v2 Plan &amp; Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Workstreams, decisions, and pre-registered acceptance criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Workstreams</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Acceptance criteria (pre-registered)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>W1. Covariate-aware forecasting</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Exogenous covariates via TimesFM 2.5 XReg (forecast_with_covariates, timesfm[xreg]). Covariate set fixed upfront: UUP (USD), CL=F (oil), HG=F (copper), all yfinance daily, no key. Future covariate values = carry-forward persistence (no lookahead).</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>PRIMARY: mean ACI-calibrated interval width at matched 90% coverage, XReg arm vs v1 cached arm on identical HRC rolling origins. SECONDARY: MASE. XReg ships only if it improves the primary without degrading coverage; else v1 stands and Moirai-2 is evaluated.</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>W2. Aluminum vertical</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>config/aluminum.yaml only (Section 232 also covers aluminum); zero code changes.</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>python -m src.pipeline --config config/aluminum.yaml runs end-to-end and produces a band-history cache + alert scan. Proves the extensibility NFR.</t>
+        </is>
+      </c>
+      <c r="D7" s="67" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>W3. Alert delivery</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Pipeline writes machine-readable alert artifacts to outputs/alerts/&lt;vertical&gt;_&lt;date&gt;.json; optional webhook URL in config (stub, off by default).</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Artifact produced on a real run; schema documented; webhook config present but inert unless set.</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>W1 backbone decision (supersedes the v1-era 'Moirai-2 for v2' note)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="74" t="inlineStr">
+        <is>
+          <t>DECISION: attempt covariates with TimesFM 2.5 XReg FIRST, keeping the proven v1 backbone, ACI calibration, and pipeline unchanged (one optional dependency: timesfm[xreg]). Moirai-2 remains the fallback, evaluated only if XReg fails to run or does not improve the pre-registered primary metric. Rationale: incremental risk, directly comparable arms on the same cached rolling origins, and no re-validation of the calibration stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="17">
+      <c r="A17" s="75" t="inlineStr">
+        <is>
+          <t>v2 evaluation principles (carried from v1)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>•  Every claim pre-registered before results are seen; nulls are published, not buried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>•  Arms compared on identical rolling origins with the same ACI settings (gamma=0.02, warmup=50).</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>•  No lookahead: future covariate values are carry-forward persistence, never realized futures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>•  Results land in this sheet + README + a step JSON before any status flips to Done.</t>
+        </is>
+      </c>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A12:D15"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A19:D19"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3527,310 +3739,332 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>v2 plan logged (sheet 12): W1 covariates via TimesFM XReg (Moirai-2 fallback), W2 aluminum vertical config-only, W3 alert delivery; W1 eval pre-registered</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>v2 In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Design Authority</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>(owner)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Overall design sign-off</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Data / ML Lead</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Model + data feasibility</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Risk Stakeholder</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Business value &amp; metrics</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="17" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Zero-shot</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Forecasting a new series with a pretrained model, no per-series retraining.</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Large pretrained time-series model (Chronos-2, TimesFM, Moirai-2).</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Conformal prediction</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Wrapper giving prediction intervals with empirically guaranteed coverage.</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>CQR</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Conformalized Quantile Regression; offsets a model's q10/q90 band to hit target coverage.</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>TimesFM 2.5</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>Google's 200M-param decoder-only time-series foundation model; zero-shot, quantile head.</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>Fraction of actuals that fall inside the predicted interval (should match nominal, e.g. 90%).</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Interval breach</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Actual value falls outside the calibrated forecast interval -&gt; candidate shock.</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Changepoint</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Statistically detected structural break in a series (via PELT / BOCPD).</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Attribution</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>Ranking candidate events to name the most likely driver of a break.</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>Early-Warning System.</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>MASE</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Mean Absolute Scaled Error; scale-free forecast accuracy vs seasonal-naive.</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>FBX</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Freightos Baltic Index (container shipping cost).</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3839,13 +4073,13 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B32:E32"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -425,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -614,6 +614,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1112,7 +1115,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>1.3 (v2 in progress)</t>
+          <t>1.4 (v2 delivered)</t>
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
@@ -1127,7 +1130,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>v1 complete and live; v2 workstreams W1-W3 planned on sheet 12</t>
+          <t>v1 + v2 complete: two live verticals, alert artifacts, covariates closed-negative</t>
         </is>
       </c>
       <c r="D17" s="8" t="n"/>
@@ -1142,7 +1145,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D18" s="8" t="n"/>
@@ -1255,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1342,7 @@
     <row r="9">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>│   └─ steel.yaml</t>
+          <t>│   ├─ steel.yaml</t>
         </is>
       </c>
       <c r="B9" s="65" t="inlineStr">
@@ -1349,492 +1352,540 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
-        <is>
-          <t>├─ src/</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="inlineStr">
-        <is>
-          <t>Application source</t>
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>│   └─ aluminum.yaml</t>
+        </is>
+      </c>
+      <c r="B10" s="63" t="inlineStr">
+        <is>
+          <t>Second vertical (ALI=F), zero code changes (v2-W2)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
         <is>
+          <t>├─ src/</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>Application source</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
           <t>│   ├─ data/</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>Ingestion layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="62" t="inlineStr">
-        <is>
-          <t>│   │   ├─ prices.py</t>
-        </is>
-      </c>
-      <c r="B12" s="63" t="inlineStr">
-        <is>
-          <t>yfinance / FRED loaders -&gt; parquet</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>│   │   ├─ trade.py</t>
+          <t>│   │   ├─ prices.py</t>
         </is>
       </c>
       <c r="B13" s="65" t="inlineStr">
         <is>
-          <t>US Census trade (HS 72xx)</t>
+          <t>yfinance / FRED loaders -&gt; parquet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ events.py</t>
+          <t>│   │   ├─ trade.py</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr">
         <is>
-          <t>Federal Register + news -&gt; normalized event table</t>
+          <t>US Census trade (HS 72xx)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="64" t="inlineStr">
         <is>
-          <t>│   │   ├─ news_tpu.py</t>
+          <t>│   │   ├─ events.py</t>
         </is>
       </c>
       <c r="B15" s="65" t="inlineStr">
         <is>
-          <t>Daily TPU index (announcement-dated events, primary)</t>
+          <t>Federal Register + news -&gt; normalized event table</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="62" t="inlineStr">
         <is>
+          <t>│   │   ├─ news_tpu.py</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>Daily TPU index (announcement-dated events, primary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
           <t>│   │   └─ news_gdelt.py</t>
         </is>
       </c>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="B17" s="65" t="inlineStr">
         <is>
           <t>GDELT volume spikes (fallback; API throttles)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>│   ├─ forecast/</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>Forecasting layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="62" t="inlineStr">
-        <is>
-          <t>│   │   ├─ timesfm_model.py</t>
-        </is>
-      </c>
-      <c r="B18" s="63" t="inlineStr">
-        <is>
-          <t>TimesFM 2.5 zero-shot forecast + quantiles (v1 default)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="64" t="inlineStr">
         <is>
-          <t>│   │   ├─ chronos_model.py</t>
+          <t>│   │   ├─ timesfm_model.py</t>
         </is>
       </c>
       <c r="B19" s="65" t="inlineStr">
         <is>
-          <t>Chronos-2 forecaster (alternative backbone)</t>
+          <t>TimesFM 2.5 zero-shot forecast + quantiles (v1 default)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>│   │   └─ conformal.py</t>
+          <t>│   │   ├─ timesfm_xreg.py</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>Split-conformal + CQR calibration wrapper</t>
+          <t>Covariate (XReg) forecaster; evaluated, does not ship (v2-W1)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
-        <is>
-          <t>│   ├─ events/</t>
-        </is>
-      </c>
-      <c r="B21" s="61" t="inlineStr">
-        <is>
-          <t>Event reasoning layer</t>
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>│   │   ├─ chronos_model.py</t>
+        </is>
+      </c>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>Chronos-2 forecaster (alternative backbone)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>│   │   ├─ embed.py</t>
+          <t>│   │   └─ conformal.py</t>
         </is>
       </c>
       <c r="B22" s="63" t="inlineStr">
         <is>
-          <t>Sentence-transformer embeddings</t>
+          <t>Split-conformal CQR + ACI calibration</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="64" t="inlineStr">
-        <is>
-          <t>│   │   ├─ severity.py</t>
-        </is>
-      </c>
-      <c r="B23" s="65" t="inlineStr">
-        <is>
-          <t>Rule-based severity tagging</t>
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>│   ├─ events/</t>
+        </is>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>Event reasoning layer</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>│   │   └─ attribute.py</t>
+          <t>│   │   ├─ embed.py</t>
         </is>
       </c>
       <c r="B24" s="63" t="inlineStr">
         <is>
-          <t>relevance x severity x recency ranking</t>
+          <t>Sentence-transformer embeddings</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr">
-        <is>
-          <t>│   ├─ detect/</t>
-        </is>
-      </c>
-      <c r="B25" s="61" t="inlineStr">
-        <is>
-          <t>Structural-break layer</t>
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>│   │   ├─ severity.py</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="inlineStr">
+        <is>
+          <t>Rule-based severity tagging</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="62" t="inlineStr">
         <is>
+          <t>│   │   └─ attribute.py</t>
+        </is>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>relevance x severity x recency ranking</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>│   ├─ detect/</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="inlineStr">
+        <is>
+          <t>Structural-break layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
           <t>│   │   └─ changepoint.py</t>
         </is>
       </c>
-      <c r="B26" s="63" t="inlineStr">
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>ruptures / BOCPD on residuals</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="64" t="inlineStr">
-        <is>
-          <t>│   ├─ pipeline.py</t>
-        </is>
-      </c>
-      <c r="B27" s="65" t="inlineStr">
-        <is>
-          <t>Orchestrates forecast -&gt; monitor -&gt; attribute -&gt; alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="60" t="inlineStr">
-        <is>
-          <t>│   └─ eval/</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="inlineStr">
-        <is>
-          <t>Evaluation layer</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
+          <t>│   ├─ pipeline.py</t>
+        </is>
+      </c>
+      <c r="B29" s="65" t="inlineStr">
+        <is>
+          <t>Orchestrates forecast -&gt; monitor -&gt; attribute -&gt; alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="60" t="inlineStr">
+        <is>
+          <t>│   └─ eval/</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>Evaluation layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="64" t="inlineStr">
+        <is>
           <t>│       ├─ backtest.py</t>
         </is>
       </c>
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>Rolling-origin; coverage, MASE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="62" t="inlineStr">
-        <is>
-          <t>│       └─ event_eval.py</t>
-        </is>
-      </c>
-      <c r="B30" s="63" t="inlineStr">
-        <is>
-          <t>Lead-time, precision/recall, attribution accuracy</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="60" t="inlineStr">
-        <is>
-          <t>├─ notebooks/</t>
-        </is>
-      </c>
-      <c r="B31" s="61" t="inlineStr">
-        <is>
-          <t>Analysis &amp; demo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>│   └─ 01_case_study_steel.ipynb</t>
+          <t>│       └─ event_eval.py</t>
         </is>
       </c>
       <c r="B32" s="63" t="inlineStr">
         <is>
-          <t>Interactive walkthrough of the production path</t>
+          <t>Lead-time, precision/recall, attribution accuracy</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>├─ tools/</t>
+          <t>├─ notebooks/</t>
         </is>
       </c>
       <c r="B33" s="61" t="inlineStr">
         <is>
-          <t>Repo meta-tooling</t>
+          <t>Analysis &amp; demo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>│   └─ build_design_doc.py</t>
+          <t>│   └─ 01_case_study_steel.ipynb</t>
         </is>
       </c>
       <c r="B34" s="63" t="inlineStr">
         <is>
-          <t>Regenerates docs/ solution design workbook</t>
+          <t>Interactive walkthrough of the production path</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="60" t="inlineStr">
         <is>
-          <t>├─ scripts/</t>
+          <t>├─ tools/</t>
         </is>
       </c>
       <c r="B35" s="61" t="inlineStr">
         <is>
-          <t>Runnable build-step scripts</t>
+          <t>Repo meta-tooling</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step1_forecast_slx.py</t>
+          <t>│   └─ build_design_doc.py</t>
         </is>
       </c>
       <c r="B36" s="63" t="inlineStr">
         <is>
-          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
+          <t>Regenerates docs/ solution design workbook</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="64" t="inlineStr">
-        <is>
-          <t>│   ├─ step2_events_attribution.py</t>
-        </is>
-      </c>
-      <c r="B37" s="65" t="inlineStr">
-        <is>
-          <t>Step 2: breach detection + Federal Register attribution</t>
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>├─ scripts/</t>
+        </is>
+      </c>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>Runnable build-step scripts</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step3_close_gaps.py</t>
+          <t>│   ├─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B38" s="63" t="inlineStr">
         <is>
-          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
+          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step4_hrc_attribution.py</t>
+          <t>│   ├─ step2_events_attribution.py</t>
         </is>
       </c>
       <c r="B39" s="65" t="inlineStr">
         <is>
-          <t>Step 4: pre-registered attribution retest on HRC futures</t>
+          <t>Step 2: breach detection + Federal Register attribution</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step5_forward_eval.py</t>
+          <t>│   ├─ step3_close_gaps.py</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
+          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step6_announcement_attribution.py</t>
+          <t>│   ├─ step4_hrc_attribution.py</t>
         </is>
       </c>
       <c r="B41" s="65" t="inlineStr">
         <is>
-          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+          <t>Step 4: pre-registered attribution retest on HRC futures</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>│   └─ step7_alert_precision.py</t>
+          <t>│   ├─ step5_forward_eval.py</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
+          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="64" t="inlineStr">
+        <is>
+          <t>│   ├─ step6_announcement_attribution.py</t>
+        </is>
+      </c>
+      <c r="B43" s="65" t="inlineStr">
+        <is>
+          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="62" t="inlineStr">
+        <is>
+          <t>│   ├─ step7_alert_precision.py</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="inlineStr">
+        <is>
           <t>Step 7: pre-specified alert-precision filter evaluation</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B43" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="60" t="inlineStr">
-        <is>
-          <t>└─ outputs/</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="inlineStr">
-        <is>
-          <t>Generated artifacts</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └─ figures/</t>
+          <t>│   └─ step8_covariates_eval.py</t>
         </is>
       </c>
       <c r="B45" s="65" t="inlineStr">
         <is>
+          <t>Step 8 (v2-W1): XReg vs v1 pre-registered eval</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="60" t="inlineStr">
+        <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="60" t="inlineStr">
+        <is>
+          <t>└─ outputs/</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="inlineStr">
+        <is>
+          <t>Generated artifacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ figures/</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="inlineStr">
+        <is>
           <t>Interval-breach plots for the writeup</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └─ alerts/</t>
+        </is>
+      </c>
+      <c r="B49" s="65" t="inlineStr">
+        <is>
+          <t>Machine-readable alert artifacts per vertical/date (v2-W3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="64" t="inlineStr">
-        <is>
-          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="62" t="inlineStr">
-        <is>
-          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
-        </is>
-      </c>
-      <c r="B49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="64" t="inlineStr">
-        <is>
-          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="62" t="inlineStr">
-        <is>
-          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
-        </is>
-      </c>
-      <c r="B51" s="36" t="n"/>
+      <c r="B51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="64" t="inlineStr">
         <is>
+          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
+        </is>
+      </c>
+      <c r="B53" s="36" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="64" t="inlineStr">
+        <is>
+          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="inlineStr">
+        <is>
+          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
+        </is>
+      </c>
+      <c r="B55" s="36" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="64" t="inlineStr">
+        <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3371,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3441,7 +3492,7 @@
       </c>
       <c r="D6" s="66" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done (negative)</t>
         </is>
       </c>
     </row>
@@ -3461,9 +3512,9 @@
           <t>python -m src.pipeline --config config/aluminum.yaml runs end-to-end and produces a band-history cache + alert scan. Proves the extensibility NFR.</t>
         </is>
       </c>
-      <c r="D7" s="67" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D7" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3483,9 +3534,9 @@
           <t>Artifact produced on a real run; schema documented; webhook config present but inert unless set.</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="D8" s="74" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3551,7 @@
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>DECISION: attempt covariates with TimesFM 2.5 XReg FIRST, keeping the proven v1 backbone, ACI calibration, and pipeline unchanged (one optional dependency: timesfm[xreg]). Moirai-2 remains the fallback, evaluated only if XReg fails to run or does not improve the pre-registered primary metric. Rationale: incremental risk, directly comparable arms on the same cached rolling origins, and no re-validation of the calibration stack.</t>
         </is>
@@ -3510,60 +3561,143 @@
     <row r="14"/>
     <row r="15"/>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>v2 measured results</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>W1 covariates (XReg)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Pre-registered eval on identical HRC origins: XReg widened ACI intervals +22.7% at matched coverage (117.3 -&gt; 143.9 USD/ton; coverage 90.0% vs 90.6%) and worsened MASE (6.85 -&gt; 8.10). XReg does NOT ship; v1 stands. Moirai-2 not pursued: the failure is the persistence-covariate information content, not the backbone; revisit only with genuinely forward-informative covariates (futures curve, inventories). step8_covariates_eval.json</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="72" t="inlineStr">
+        <is>
+          <t>Done (negative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>W2 aluminum vertical</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>config/aluminum.yaml (ALI=F) ran end-to-end with ZERO code changes: own band-history cache, event table, ACI scan, alert artifact. Extensibility NFR proven.</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>W3 alert delivery</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>deliver() writes outputs/alerts/&lt;vertical&gt;_&lt;date&gt;.json on every run (zero-alert runs distinguishable from no-run); candidate-drivers schema embeds the 'not a causal claim' note; webhook config-driven, inert by default, failures cannot kill the batch. Verified on steel and aluminum runs.</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>v2 evaluation principles (carried from v1)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>•  Every claim pre-registered before results are seen; nulls are published, not buried.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>•  Arms compared on identical rolling origins with the same ACI settings (gamma=0.02, warmup=50).</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>•  No lookahead: future covariate values are carry-forward persistence, never realized futures.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>•  Results land in this sheet + README + a step JSON before any status flips to Done.</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A12:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3576,7 +3710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3761,310 +3895,332 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>v2 delivered: W1 closed-negative (XReg +22.7% width, does not ship; v1 stands), W2 aluminum vertical live config-only, W3 alert artifacts + inert webhook shipped</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>v2 Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Design Authority</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>(owner)</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Overall design sign-off</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Data / ML Lead</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Model + data feasibility</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Risk Stakeholder</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>(TBD)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Business value &amp; metrics</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Glossary</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="17" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Zero-shot</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Forecasting a new series with a pretrained model, no per-series retraining.</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Foundation model</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Large pretrained time-series model (Chronos-2, TimesFM, Moirai-2).</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Conformal prediction</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Wrapper giving prediction intervals with empirically guaranteed coverage.</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>CQR</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Conformalized Quantile Regression; offsets a model's q10/q90 band to hit target coverage.</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>TimesFM 2.5</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Google's 200M-param decoder-only time-series foundation model; zero-shot, quantile head.</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Fraction of actuals that fall inside the predicted interval (should match nominal, e.g. 90%).</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Interval breach</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Actual value falls outside the calibrated forecast interval -&gt; candidate shock.</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Changepoint</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Statistically detected structural break in a series (via PELT / BOCPD).</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Attribution</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Ranking candidate events to name the most likely driver of a break.</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Early-Warning System.</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>MASE</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>Mean Absolute Scaled Error; scale-free forecast accuracy vs seasonal-naive.</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>FBX</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Freightos Baltic Index (container shipping cost).</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4072,6 +4228,7 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
@@ -4081,7 +4238,6 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B22:E22"/>
     <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3422,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3683,14 +3683,157 @@
       <c r="C28" s="36" t="n"/>
       <c r="D28" s="36" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>Post-v2 gap register (found in the v2 close-out audit; solve in order)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Risk if left open</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>G1. No automated tests for core quant logic</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Regressions in CQR/ACI math, severity rules, attribution ranking, or the alert schema ship silently; all verification so far was manual</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>pytest suite: synthetic coverage-guarantee tests for cqr_offset/aci_cqr, rule tests for severity, stub-embedder tests for attribution, schema test for deliver()</t>
+        </is>
+      </c>
+      <c r="D32" s="66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>G2. Aluminum calibration unvalidated</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>W2 proved the pipeline RUNS on ALI=F, not that ACI holds ~90% coverage there; alerts on an uncalibrated vertical are untrustworthy</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Run ACI over the cached bands_aluminum.parquet; record realized coverage here</t>
+        </is>
+      </c>
+      <c r="D33" s="66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>G3. ACI gamma=0.02 is an untested default</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>A lucky constant: calibration quality could hinge on one literature value never checked on our series</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Sweep gamma in {0.005, 0.01, 0.02, 0.05, 0.1} on cached HRC + SLX bands. Pre-registered: keep 0.02 unless another value clearly dominates |coverage-90| on BOTH series</t>
+        </is>
+      </c>
+      <c r="D34" s="66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>G4. Band cache lacks a config guard</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Changing horizon_days or the target symbol silently feeds stale cached bands into ACI (wrong intervals, no error)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Sidecar meta (symbol, horizon, quantiles) written with the cache; mismatch invalidates and recomputes; unit test</t>
+        </is>
+      </c>
+      <c r="D35" s="66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>G5. No scheduled execution</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>The 'daily batch' only runs when someone remembers; stale alerts read as 'all clear'</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_daily.bat for both verticals + README ops note with the Windows Task Scheduler registration command</t>
+        </is>
+      </c>
+      <c r="D36" s="66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A12:D15"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A24:D24"/>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3728,12 +3728,12 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>pytest suite: synthetic coverage-guarantee tests for cqr_offset/aci_cqr, rule tests for severity, stub-embedder tests for attribution, schema test for deliver()</t>
-        </is>
-      </c>
-      <c r="D32" s="66" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>pytest suite: synthetic coverage-guarantee tests for cqr_offset/aci_cqr (incl. regime-shift adaptation + negative-offset tightening), rule tests for severity, stub-embedder tests for attribution (incl. the object-dtype regression), event_eval metrics, deliver() schema + webhook-failure isolation. 25 tests green, network-free.</t>
+        </is>
+      </c>
+      <c r="D32" s="74" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3750,12 +3750,12 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>Run ACI over the cached bands_aluminum.parquet; record realized coverage here</t>
-        </is>
-      </c>
-      <c r="D33" s="66" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Validated (step9): ACI realized coverage 89.6% vs 90% target over 550 post-warmup days (2024-03..2026-07), 57 breach-days, mean calibrated width 300.7 USD/ton. Small-sample caveat noted; coverage continues to be monitored on every alert.</t>
+        </is>
+      </c>
+      <c r="D33" s="74" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Sweep gamma in {0.005, 0.01, 0.02, 0.05, 0.1} on cached HRC + SLX bands. Pre-registered: keep 0.02 unless another value clearly dominates |coverage-90| on BOTH series</t>
-        </is>
-      </c>
-      <c r="D34" s="66" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Swept (step10): coverage within ~0.5pp of target for gamma 0.005-0.05 on BOTH series (HRC 89.6-90.2%, SLX 89.2-89.7%); only gamma=0.1 degrades (&gt;1pp). No challenger dominates; 0.02 KEPT per the pre-registered rule. The default is robust, not lucky.</t>
+        </is>
+      </c>
+      <c r="D34" s="74" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>Sidecar meta (symbol, horizon, quantiles) written with the cache; mismatch invalidates and recomputes; unit test</t>
-        </is>
-      </c>
-      <c r="D35" s="66" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Implemented: sidecar bands_&lt;vertical&gt;.meta.json (symbol, horizon, quantiles) written with the cache; mismatch or missing meta invalidates and recomputes with a printed notice. 4 unit tests (hit, horizon change, symbol change, pre-guard cache). One-time recompute of existing caches.</t>
+        </is>
+      </c>
+      <c r="D35" s="74" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>

--- a/docs/Tariff_Shock_EWS_Solution_Design.xlsx
+++ b/docs/Tariff_Shock_EWS_Solution_Design.xlsx
@@ -1258,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1654,223 +1654,271 @@
     <row r="35">
       <c r="A35" s="60" t="inlineStr">
         <is>
+          <t>├─ tests/</t>
+        </is>
+      </c>
+      <c r="B35" s="61" t="inlineStr">
+        <is>
+          <t>pytest suite: conformal math, events, eval, delivery, cache guard (G1/G4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="inlineStr">
+        <is>
           <t>├─ tools/</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>Repo meta-tooling</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>│   └─ build_design_doc.py</t>
         </is>
       </c>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>Regenerates docs/ solution design workbook</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="60" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>├─ scripts/</t>
         </is>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>Runnable build-step scripts</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="62" t="inlineStr">
-        <is>
-          <t>│   ├─ step1_forecast_slx.py</t>
-        </is>
-      </c>
-      <c r="B38" s="63" t="inlineStr">
-        <is>
-          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step2_events_attribution.py</t>
+          <t>│   ├─ step1_forecast_slx.py</t>
         </is>
       </c>
       <c r="B39" s="65" t="inlineStr">
         <is>
-          <t>Step 2: breach detection + Federal Register attribution</t>
+          <t>Step 1: SLX TimesFM forecast + CQR interval + baselines</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step3_close_gaps.py</t>
+          <t>│   ├─ step2_events_attribution.py</t>
         </is>
       </c>
       <c r="B40" s="63" t="inlineStr">
         <is>
-          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
+          <t>Step 2: breach detection + Federal Register attribution</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step4_hrc_attribution.py</t>
+          <t>│   ├─ step3_close_gaps.py</t>
         </is>
       </c>
       <c r="B41" s="65" t="inlineStr">
         <is>
-          <t>Step 4: pre-registered attribution retest on HRC futures</t>
+          <t>Step 3: ACI, GARCH baseline, frozen holdout, permutation test</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step5_forward_eval.py</t>
+          <t>│   ├─ step4_hrc_attribution.py</t>
         </is>
       </c>
       <c r="B42" s="63" t="inlineStr">
         <is>
-          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
+          <t>Step 4: pre-registered attribution retest on HRC futures</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="64" t="inlineStr">
         <is>
-          <t>│   ├─ step6_announcement_attribution.py</t>
+          <t>│   ├─ step5_forward_eval.py</t>
         </is>
       </c>
       <c r="B43" s="65" t="inlineStr">
         <is>
-          <t>Step 6: announcement-dated (TPU) attribution retest</t>
+          <t>Step 5: forward early-warning eval (G3), ACI flags vs shocks</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="62" t="inlineStr">
         <is>
-          <t>│   ├─ step7_alert_precision.py</t>
+          <t>│   ├─ step6_announcement_attribution.py</t>
         </is>
       </c>
       <c r="B44" s="63" t="inlineStr">
         <is>
-          <t>Step 7: pre-specified alert-precision filter evaluation</t>
+          <t>Step 6: announcement-dated (TPU) attribution retest</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="64" t="inlineStr">
         <is>
-          <t>│   └─ step8_covariates_eval.py</t>
+          <t>│   ├─ step7_alert_precision.py</t>
         </is>
       </c>
       <c r="B45" s="65" t="inlineStr">
         <is>
+          <t>Step 7: pre-specified alert-precision filter evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="62" t="inlineStr">
+        <is>
+          <t>│   ├─ step8_covariates_eval.py</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="inlineStr">
+        <is>
           <t>Step 8 (v2-W1): XReg vs v1 pre-registered eval</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="60" t="inlineStr">
-        <is>
-          <t>├─ data/</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="inlineStr">
-        <is>
-          <t>Gitignored raw + parquet cache</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="60" t="inlineStr">
-        <is>
-          <t>└─ outputs/</t>
-        </is>
-      </c>
-      <c r="B47" s="61" t="inlineStr">
-        <is>
-          <t>Generated artifacts</t>
+      <c r="A47" s="64" t="inlineStr">
+        <is>
+          <t>│   ├─ step9_aluminum_validation.py</t>
+        </is>
+      </c>
+      <c r="B47" s="65" t="inlineStr">
+        <is>
+          <t>Step 9 (G2): aluminum ACI coverage validation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ├─ figures/</t>
+          <t>│   ├─ step10_gamma_sweep.py</t>
         </is>
       </c>
       <c r="B48" s="63" t="inlineStr">
         <is>
-          <t>Interval-breach plots for the writeup</t>
+          <t>Step 10 (G3): ACI gamma sensitivity sweep</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="64" t="inlineStr">
         <is>
+          <t>│   └─ run_daily.bat</t>
+        </is>
+      </c>
+      <c r="B49" s="65" t="inlineStr">
+        <is>
+          <t>Daily batch for all verticals + logs (G5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="60" t="inlineStr">
+        <is>
+          <t>├─ data/</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
+          <t>Gitignored raw + parquet cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="60" t="inlineStr">
+        <is>
+          <t>└─ outputs/</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="inlineStr">
+        <is>
+          <t>Generated artifacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ├─ figures/</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="inlineStr">
+        <is>
+          <t>Interval-breach plots for the writeup</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="64" t="inlineStr">
+        <is>
           <t xml:space="preserve">    └─ alerts/</t>
         </is>
       </c>
-      <c r="B49" s="65" t="inlineStr">
+      <c r="B53" s="65" t="inlineStr">
         <is>
           <t>Machine-readable alert artifacts per vertical/date (v2-W3)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Recommended build order (always keep something working)</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="64" t="inlineStr">
-        <is>
-          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="62" t="inlineStr">
-        <is>
-          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
-        </is>
-      </c>
-      <c r="B53" s="36" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="64" t="inlineStr">
-        <is>
-          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="62" t="inlineStr">
-        <is>
-          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
-        </is>
-      </c>
-      <c r="B55" s="36" t="n"/>
+      <c r="B55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="64" t="inlineStr">
+        <is>
+          <t>1. data/prices.py + forecast/chronos_model.py  -&gt;  a zero-shot forecast plotted (Day 1-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
+        <is>
+          <t>2. forecast/conformal.py + eval/backtest.py     -&gt;  calibrated intervals + coverage (Day 3-4)</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>3. data/events.py + events/*                     -&gt;  event table + attribution (Day 5-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="inlineStr">
+        <is>
+          <t>4. eval/event_eval.py on real 2025-26 events     -&gt;  the money chart (Day 8-9)</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="64" t="inlineStr">
         <is>
           <t>5. notebooks/01 + README case study             -&gt;  the shareable artifact (Day 10)</t>
         </is>
@@ -1879,12 +1927,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3816,12 +3864,12 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>scripts/run_daily.bat for both verticals + README ops note with the Windows Task Scheduler registration command</t>
-        </is>
-      </c>
-      <c r="D36" s="66" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Implemented: scripts/run_daily.bat runs every vertical with per-vertical logs (outputs/logs/); README Operations section documents the schtasks registration. Verified end-to-end on both verticals; missing daily artifact now means 'did not run', never 'all clear'.</t>
+        </is>
+      </c>
+      <c r="D36" s="74" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>
